--- a/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_pendientes.xlsx
+++ b/DATA/MASTER/C11_MASTER/Preparacion_Machine_Learning/ipm/variables_pendientes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,44 +486,44 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Importancia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Conocimiento_Dominio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>% Cobertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Calidad</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Redundancia</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Multicolinealidad</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IPML</t>
@@ -537,12 +537,17 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Estado_Final</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Justificacion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -567,11 +572,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.027</v>
+        <v>1.028</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -580,41 +585,41 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Hidrológica</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>16.48</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.165</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0.9165</v>
@@ -627,12 +632,17 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>Pendiente por Cobertura</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -657,11 +667,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.815</v>
+        <v>2.878</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -670,41 +680,41 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.095</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0.9095</v>
@@ -717,12 +727,17 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>Pendiente por Cobertura</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -747,11 +762,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.97</v>
+        <v>2.999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -760,41 +775,41 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.093</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0.9093</v>
@@ -807,16 +822,21 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>Pendiente por Cobertura</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGUAS RESIDUALES TRATADAS</t>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -825,10 +845,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -837,11 +857,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.63</v>
+        <v>1.965</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -850,63 +870,68 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.833</v>
+        <v>4.92</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.049</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8681</v>
+        <v>0.9049</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>Pendiente por Cobertura</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CALIDAD DEL AGUA</t>
+          <t>OXIGENO DISUELTO (OD)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -915,69 +940,69 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Muy Baja</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Baja redundancia estructural.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.372</v>
+        <v>7.54</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Muy Alta</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0.667</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8183</v>
+        <v>0.8595</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -989,184 +1014,9 @@
           <t>Pendiente por Cobertura</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>OXIGENO DISUELTO (OD)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Numérica</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Muy Baja</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7.427</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Moderada</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.8094</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Pendiente por Cobertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Numérica</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1.934</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Pendiente por Cobertura</t>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Cobertura inferior al umbral mínimo establecido.</t>
         </is>
       </c>
     </row>
